--- a/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
+++ b/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jake Truscott\Documents\GitHub\jaketruscott.github.io\_scotuswatch\ot23_decisions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469C6B2D-597A-434C-905A-4EA7A90E5298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23294746-364C-480B-A7EF-54623A396F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="0" windowWidth="24270" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
+    <workbookView xWindow="-24285" yWindow="975" windowWidth="25425" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>Case</t>
   </si>
@@ -99,6 +99,48 @@
   </si>
   <si>
     <t>CA1</t>
+  </si>
+  <si>
+    <t>Murray v. UBS Securities, LLC</t>
+  </si>
+  <si>
+    <t>Department of Agriculture Rural Development Rural Housing Service v. Kirtz</t>
+  </si>
+  <si>
+    <t>Great Lakes Ins. SE v. Raiders Retreat Reality Co.</t>
+  </si>
+  <si>
+    <t>McElrath v. Georgia</t>
+  </si>
+  <si>
+    <t>CA2</t>
+  </si>
+  <si>
+    <t>CA3</t>
+  </si>
+  <si>
+    <t>SCGA</t>
+  </si>
+  <si>
+    <t>Reverse and Remand</t>
+  </si>
+  <si>
+    <t>Affirm</t>
+  </si>
+  <si>
+    <t>Reverse</t>
+  </si>
+  <si>
+    <t>Sotomayor</t>
+  </si>
+  <si>
+    <t>Gorsuch</t>
+  </si>
+  <si>
+    <t>Kavanaugh</t>
+  </si>
+  <si>
+    <t>Jackson</t>
   </si>
 </sst>
 </file>
@@ -155,9 +197,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -195,7 +237,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -301,7 +343,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -443,7 +485,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -451,9 +493,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575911E7-0238-4920-9169-BE957B59E37F}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="4" width="15.140625" customWidth="1"/>
     <col min="11" max="11" width="12.42578125" customWidth="1"/>
   </cols>
@@ -534,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -555,7 +598,207 @@
         <v>100</v>
       </c>
       <c r="P2">
-        <v>4</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45208</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45329</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
+        <v>45235</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45329</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1">
+        <v>45208</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45342</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45247</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45342</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
+++ b/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jake Truscott\Documents\GitHub\jaketruscott.github.io\_scotuswatch\ot23_decisions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23294746-364C-480B-A7EF-54623A396F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188492F1-23E5-424E-AA71-27A981705920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24285" yWindow="975" windowWidth="25425" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
+    <workbookView xWindow="-22680" yWindow="300" windowWidth="25425" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>Case</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>Jackson</t>
+  </si>
+  <si>
+    <t>Trump v. Anderson</t>
+  </si>
+  <si>
+    <t>SCCO</t>
+  </si>
+  <si>
+    <t>Per Curiam</t>
   </si>
 </sst>
 </file>
@@ -493,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575911E7-0238-4920-9169-BE957B59E37F}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -801,6 +810,56 @@
         <v>100</v>
       </c>
     </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45330</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45355</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>7</v>
+      </c>
+      <c r="P7">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
+++ b/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jake Truscott\Documents\GitHub\jaketruscott.github.io\_scotuswatch\ot23_decisions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188492F1-23E5-424E-AA71-27A981705920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC7AF7F-6769-431D-8958-2205049459F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22680" yWindow="300" windowWidth="25425" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
+    <workbookView xWindow="7845" yWindow="195" windowWidth="19140" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>Case</t>
   </si>
@@ -150,6 +150,30 @@
   </si>
   <si>
     <t>Per Curiam</t>
+  </si>
+  <si>
+    <t>CA9</t>
+  </si>
+  <si>
+    <t>O'Connor-Ratcliff v. Garnier</t>
+  </si>
+  <si>
+    <t>Lindke v. Freed</t>
+  </si>
+  <si>
+    <t>CA6</t>
+  </si>
+  <si>
+    <t>Pulsifer v. United States</t>
+  </si>
+  <si>
+    <t>CA8</t>
+  </si>
+  <si>
+    <t>Kagan</t>
+  </si>
+  <si>
+    <t>(6-3)</t>
   </si>
 </sst>
 </file>
@@ -502,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575911E7-0238-4920-9169-BE957B59E37F}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -860,6 +884,156 @@
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="1">
+        <v>45230</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45366</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45230</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45366</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1">
+        <v>45201</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45366</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>-2</v>
+      </c>
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10">
+        <v>-1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
+++ b/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jake Truscott\Documents\GitHub\jaketruscott.github.io\_scotuswatch\ot23_decisions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC7AF7F-6769-431D-8958-2205049459F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1E3AA2-EDF8-486D-9767-567EF430A200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7845" yWindow="195" windowWidth="19140" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
+    <workbookView xWindow="8370" yWindow="30" windowWidth="18300" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
   <si>
     <t>Case</t>
   </si>
@@ -174,6 +174,15 @@
   </si>
   <si>
     <t>(6-3)</t>
+  </si>
+  <si>
+    <t>Wilkinson v. Garland</t>
+  </si>
+  <si>
+    <t>Reverse In Part, Vacate In Part, Remand</t>
+  </si>
+  <si>
+    <t>FBI v. Fikre</t>
   </si>
 </sst>
 </file>
@@ -526,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575911E7-0238-4920-9169-BE957B59E37F}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1034,6 +1043,106 @@
         <v>-2</v>
       </c>
     </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1">
+        <v>45258</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45370</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11">
+        <v>-3</v>
+      </c>
+      <c r="I11">
+        <v>-2</v>
+      </c>
+      <c r="J11">
+        <v>-1</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1">
+        <v>45299</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45370</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
+++ b/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jake Truscott\Documents\GitHub\jaketruscott.github.io\_scotuswatch\ot23_decisions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1E3AA2-EDF8-486D-9767-567EF430A200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65930F6-64B2-497B-B808-9ACC0F203AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8370" yWindow="30" windowWidth="18300" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
+    <workbookView xWindow="8940" yWindow="795" windowWidth="19035" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
   <si>
     <t>Case</t>
   </si>
@@ -183,6 +183,21 @@
   </si>
   <si>
     <t>FBI v. Fikre</t>
+  </si>
+  <si>
+    <t>Bissonnette v. LePage Bakeries Park St., LLC</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>Macquarie Infrastructure Corp. v. Moab Partners</t>
+  </si>
+  <si>
+    <t>Sheetz v. County of El Dorado, California</t>
+  </si>
+  <si>
+    <t>Cal. Ct. App.</t>
   </si>
 </sst>
 </file>
@@ -535,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575911E7-0238-4920-9169-BE957B59E37F}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1143,6 +1158,156 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45342</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45394</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="1">
+        <v>45307</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45394</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="1">
+        <v>45300</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45394</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
+++ b/_scotuswatch/ot23_decisions/OT_23_Decisions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jake Truscott\Documents\GitHub\jaketruscott.github.io\_scotuswatch\ot23_decisions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65930F6-64B2-497B-B808-9ACC0F203AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C1C879-0B65-4E83-98DB-0BF2BFDC280B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="795" windowWidth="19035" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
+    <workbookView xWindow="825" yWindow="0" windowWidth="25425" windowHeight="15600" xr2:uid="{75691BF7-3144-4BA8-BFE8-D6F908DA101F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t>Case</t>
   </si>
@@ -198,6 +198,51 @@
   </si>
   <si>
     <t>Cal. Ct. App.</t>
+  </si>
+  <si>
+    <t>Docket</t>
+  </si>
+  <si>
+    <t>22-429</t>
+  </si>
+  <si>
+    <t>22-660</t>
+  </si>
+  <si>
+    <t>22-846</t>
+  </si>
+  <si>
+    <t>22-500</t>
+  </si>
+  <si>
+    <t>22-721</t>
+  </si>
+  <si>
+    <t>23-719</t>
+  </si>
+  <si>
+    <t>22-324</t>
+  </si>
+  <si>
+    <t>22-611</t>
+  </si>
+  <si>
+    <t>22-340</t>
+  </si>
+  <si>
+    <t>22-666</t>
+  </si>
+  <si>
+    <t>22-1178</t>
+  </si>
+  <si>
+    <t>23-51</t>
+  </si>
+  <si>
+    <t>22-1165</t>
+  </si>
+  <si>
+    <t>22-1074</t>
   </si>
 </sst>
 </file>
@@ -550,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575911E7-0238-4920-9169-BE957B59E37F}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -558,7 +603,7 @@
     <col min="11" max="11" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,8 +652,11 @@
       <c r="P1" t="s">
         <v>11</v>
       </c>
+      <c r="Q1" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -657,8 +705,11 @@
       <c r="P2">
         <v>5</v>
       </c>
+      <c r="Q2" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -707,8 +758,11 @@
       <c r="P3">
         <v>1</v>
       </c>
+      <c r="Q3" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -757,8 +811,11 @@
       <c r="P4">
         <v>1</v>
       </c>
+      <c r="Q4" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -807,8 +864,11 @@
       <c r="P5">
         <v>1</v>
       </c>
+      <c r="Q5" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -857,8 +917,11 @@
       <c r="P6">
         <v>100</v>
       </c>
+      <c r="Q6" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -907,8 +970,11 @@
       <c r="P7">
         <v>6</v>
       </c>
+      <c r="Q7" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -957,8 +1023,11 @@
       <c r="P8">
         <v>1</v>
       </c>
+      <c r="Q8" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1007,8 +1076,11 @@
       <c r="P9">
         <v>1</v>
       </c>
+      <c r="Q9" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1057,8 +1129,11 @@
       <c r="P10">
         <v>-2</v>
       </c>
+      <c r="Q10" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -1107,8 +1182,11 @@
       <c r="P11">
         <v>5</v>
       </c>
+      <c r="Q11" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1157,8 +1235,11 @@
       <c r="P12">
         <v>1</v>
       </c>
+      <c r="Q12" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -1207,8 +1288,11 @@
       <c r="P13">
         <v>1</v>
       </c>
+      <c r="Q13" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1257,8 +1341,11 @@
       <c r="P14">
         <v>1</v>
       </c>
+      <c r="Q14" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1306,6 +1393,9 @@
       </c>
       <c r="P15">
         <v>3</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
